--- a/AAII_Financials/Yearly/CHCO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CHCO_YR_FIN.xlsx
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>402000</v>
+        <v>403200</v>
       </c>
       <c r="E58" s="3">
         <v>376900</v>
@@ -3074,7 +3074,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>5703000</v>
+        <v>5704100</v>
       </c>
       <c r="E60" s="3">
         <v>5521100</v>
@@ -3125,7 +3125,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>150000</v>
+        <v>157600</v>
       </c>
       <c r="E61" s="3">
         <v>150000</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>55000</v>
+        <v>46300</v>
       </c>
       <c r="E62" s="3">
         <v>53100</v>
